--- a/dcf/CDNS.xlsx
+++ b/dcf/CDNS.xlsx
@@ -859,7 +859,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1141,25 +1141,25 @@
         <v>19</v>
       </c>
       <c r="B5" s="54" t="n">
-        <v>185.0184000144359</v>
+        <v>164.2291473435549</v>
       </c>
       <c r="C5" s="54" t="n">
-        <v>177.5287905118988</v>
+        <v>157.6341458341902</v>
       </c>
       <c r="D5" s="54" t="n">
-        <v>170.3916559382091</v>
+        <v>151.3485453858912</v>
       </c>
       <c r="E5" s="54" t="n">
-        <v>163.5885613810101</v>
+        <v>145.3561856041632</v>
       </c>
       <c r="F5" s="54" t="n">
-        <v>157.1021222122479</v>
+        <v>139.6418261608994</v>
       </c>
       <c r="G5" s="54" t="n">
-        <v>150.9159395982932</v>
+        <v>134.1910903225198</v>
       </c>
       <c r="H5" s="54" t="n">
-        <v>145.0145402469634</v>
+        <v>128.9904121873222</v>
       </c>
     </row>
     <row r="6">
@@ -1167,25 +1167,25 @@
         <v>20</v>
       </c>
       <c r="B6" s="54" t="n">
-        <v>192.1578058443879</v>
+        <v>170.4749130619275</v>
       </c>
       <c r="C6" s="54" t="n">
-        <v>184.345816405278</v>
+        <v>163.5978839435297</v>
       </c>
       <c r="D6" s="54" t="n">
-        <v>176.9022424487819</v>
+        <v>157.0442011593224</v>
       </c>
       <c r="E6" s="54" t="n">
-        <v>169.8077930640372</v>
+        <v>150.7969554617198</v>
       </c>
       <c r="F6" s="54" t="n">
-        <v>163.0442771990752</v>
+        <v>144.8402010388591</v>
       </c>
       <c r="G6" s="54" t="n">
-        <v>156.5945360927693</v>
+        <v>139.1588963498609</v>
       </c>
       <c r="H6" s="54" t="n">
-        <v>150.4423801475588</v>
+        <v>133.738848847657</v>
       </c>
     </row>
     <row r="7">
@@ -1193,25 +1193,25 @@
         <v>21</v>
       </c>
       <c r="B7" s="54" t="n">
-        <v>199.29721167434</v>
+        <v>176.7206787803</v>
       </c>
       <c r="C7" s="54" t="n">
-        <v>191.1628422986572</v>
+        <v>169.5616220528692</v>
       </c>
       <c r="D7" s="54" t="n">
-        <v>183.4128289593548</v>
+        <v>162.7398569327536</v>
       </c>
       <c r="E7" s="54" t="n">
-        <v>176.0270247470644</v>
+        <v>156.2377253192764</v>
       </c>
       <c r="F7" s="54" t="n">
-        <v>168.9864321859024</v>
+        <v>150.0385759168188</v>
       </c>
       <c r="G7" s="54" t="n">
-        <v>162.2731325872455</v>
+        <v>144.126702377202</v>
       </c>
       <c r="H7" s="54" t="n">
-        <v>155.8702200481541</v>
+        <v>138.4872855079919</v>
       </c>
     </row>
     <row r="8">
@@ -1219,25 +1219,25 @@
         <v>22</v>
       </c>
       <c r="B8" s="54" t="n">
-        <v>206.4366175042921</v>
+        <v>182.9664444986726</v>
       </c>
       <c r="C8" s="54" t="n">
-        <v>197.9798681920363</v>
+        <v>175.5253601622086</v>
       </c>
       <c r="D8" s="54" t="n">
-        <v>189.9234154699277</v>
+        <v>168.4355127061847</v>
       </c>
       <c r="E8" s="55" t="n">
-        <v>182.2462564300915</v>
+        <v>161.6784951768331</v>
       </c>
       <c r="F8" s="54" t="n">
-        <v>174.9285871727296</v>
+        <v>155.2369507947786</v>
       </c>
       <c r="G8" s="54" t="n">
-        <v>167.9517290817217</v>
+        <v>149.094508404543</v>
       </c>
       <c r="H8" s="54" t="n">
-        <v>161.2980599487494</v>
+        <v>143.2357221683268</v>
       </c>
     </row>
     <row r="9">
@@ -1245,25 +1245,25 @@
         <v>23</v>
       </c>
       <c r="B9" s="54" t="n">
-        <v>213.5760233342441</v>
+        <v>189.2122102170451</v>
       </c>
       <c r="C9" s="54" t="n">
-        <v>204.7968940854155</v>
+        <v>181.4890982715481</v>
       </c>
       <c r="D9" s="54" t="n">
-        <v>196.4340019805006</v>
+        <v>174.131168479616</v>
       </c>
       <c r="E9" s="54" t="n">
-        <v>188.4654881131187</v>
+        <v>167.1192650343897</v>
       </c>
       <c r="F9" s="54" t="n">
-        <v>180.8707421595569</v>
+        <v>160.4353256727383</v>
       </c>
       <c r="G9" s="54" t="n">
-        <v>173.6303255761979</v>
+        <v>154.0623144318841</v>
       </c>
       <c r="H9" s="54" t="n">
-        <v>166.7258998493448</v>
+        <v>147.9841588286617</v>
       </c>
     </row>
     <row r="10">
@@ -1271,25 +1271,25 @@
         <v>24</v>
       </c>
       <c r="B10" s="54" t="n">
-        <v>220.7154291641962</v>
+        <v>195.4579759354177</v>
       </c>
       <c r="C10" s="54" t="n">
-        <v>211.6139199787947</v>
+        <v>187.4528363808876</v>
       </c>
       <c r="D10" s="54" t="n">
-        <v>202.9445884910734</v>
+        <v>179.8268242530472</v>
       </c>
       <c r="E10" s="54" t="n">
-        <v>194.6847197961458</v>
+        <v>172.5600348919463</v>
       </c>
       <c r="F10" s="54" t="n">
-        <v>186.8128971463841</v>
+        <v>165.6337005506981</v>
       </c>
       <c r="G10" s="54" t="n">
-        <v>179.308922070674</v>
+        <v>159.0301204592252</v>
       </c>
       <c r="H10" s="54" t="n">
-        <v>172.1537397499401</v>
+        <v>152.7325954889966</v>
       </c>
     </row>
     <row r="11">
@@ -1297,25 +1297,25 @@
         <v>25</v>
       </c>
       <c r="B11" s="54" t="n">
-        <v>227.8548349941482</v>
+        <v>201.7037416537902</v>
       </c>
       <c r="C11" s="54" t="n">
-        <v>218.4309458721738</v>
+        <v>193.4165744902271</v>
       </c>
       <c r="D11" s="54" t="n">
-        <v>209.4551750016463</v>
+        <v>185.5224800264783</v>
       </c>
       <c r="E11" s="54" t="n">
-        <v>200.9039514791729</v>
+        <v>178.000804749503</v>
       </c>
       <c r="F11" s="54" t="n">
-        <v>192.7550521332113</v>
+        <v>170.8320754286578</v>
       </c>
       <c r="G11" s="54" t="n">
-        <v>184.9875185651502</v>
+        <v>163.9979264865663</v>
       </c>
       <c r="H11" s="54" t="n">
-        <v>177.5815796505353</v>
+        <v>157.4810321493315</v>
       </c>
     </row>
     <row r="13">
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="I8" s="49" t="n">
-        <v>0.9089976754885069</v>
+        <v>0.9093535383535973</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24446,7 +24446,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24598,13 +24598,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>182.2462564300915</v>
+        <v>161.6784951768331</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>244.1148380830628</v>
+        <v>211.379429034578</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>134.7833647916034</v>
+        <v>122.5443406481599</v>
       </c>
     </row>
     <row r="59">
